--- a/artfynd/A 74075-2021 artfynd.xlsx
+++ b/artfynd/A 74075-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 74075-2021 artfynd.xlsx
+++ b/artfynd/A 74075-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91502067</v>
+        <v>100212646</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bryningen, Dlr</t>
+          <t>Översjökölen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421280.8013431299</v>
+        <v>421390</v>
       </c>
       <c r="R2" t="n">
-        <v>6841762.725498062</v>
+        <v>6841805</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +761,11 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Urskogsartad myr</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -784,22 +774,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Andreas Öster, John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100212713</v>
+        <v>100212647</v>
       </c>
       <c r="B3" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,16 +810,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Översjökölen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421432.8900641685</v>
+        <v>421409</v>
       </c>
       <c r="R3" t="n">
-        <v>6841950.01714081</v>
+        <v>6841678</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,29 +852,25 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Urskogsartad myr</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -896,22 +880,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Andreas Öster, John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100212741</v>
+        <v>100212667</v>
       </c>
       <c r="B4" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>967</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421439.2850259623</v>
+        <v>421474</v>
       </c>
       <c r="R4" t="n">
-        <v>6841855.437591757</v>
+        <v>6841886</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -976,19 +955,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,12 +987,7 @@
         <v>100212684</v>
       </c>
       <c r="B5" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421400.649521723</v>
+        <v>421401</v>
       </c>
       <c r="R5" t="n">
-        <v>6841890.961742317</v>
+        <v>6841891</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,19 +1052,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1081,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100212701</v>
+        <v>100212687</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1092,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421459.6796887669</v>
+        <v>421376</v>
       </c>
       <c r="R6" t="n">
-        <v>6841874.428332214</v>
+        <v>6841803</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1200,19 +1149,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,15 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100212705</v>
+        <v>100212689</v>
       </c>
       <c r="B7" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,10 +1213,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421451.4602670872</v>
+        <v>421323</v>
       </c>
       <c r="R7" t="n">
-        <v>6841493.536080766</v>
+        <v>6841682</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1312,19 +1246,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,15 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100212688</v>
+        <v>100212705</v>
       </c>
       <c r="B8" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,21 +1286,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>967</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1310,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>421426.5554557114</v>
+        <v>421452</v>
       </c>
       <c r="R8" t="n">
-        <v>6841839.119095862</v>
+        <v>6841493</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1424,19 +1343,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,15 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100212667</v>
+        <v>100212713</v>
       </c>
       <c r="B9" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421473.7149349835</v>
+        <v>421433</v>
       </c>
       <c r="R9" t="n">
-        <v>6841885.497005603</v>
+        <v>6841950</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1536,19 +1440,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,15 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>100212758</v>
+        <v>100212747</v>
       </c>
       <c r="B10" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421354.3285638297</v>
+        <v>421534</v>
       </c>
       <c r="R10" t="n">
-        <v>6841590.198126952</v>
+        <v>6842018</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1648,19 +1537,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,15 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>100212647</v>
+        <v>100212758</v>
       </c>
       <c r="B11" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,19 +1595,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Översjökölen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>421409.5714573654</v>
+        <v>421355</v>
       </c>
       <c r="R11" t="n">
-        <v>6841678.156511979</v>
+        <v>6841590</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,35 +1634,19 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Urskogsartad myr</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1801,22 +1656,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Andreas Öster, John-Olof Halvarsson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>100212747</v>
+        <v>100212741</v>
       </c>
       <c r="B12" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,21 +1674,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>967</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1848,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>421534.2528343103</v>
+        <v>421439</v>
       </c>
       <c r="R12" t="n">
-        <v>6842018.408662979</v>
+        <v>6841855</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1881,19 +1731,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,50 +1760,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>100212669</v>
+        <v>91502067</v>
       </c>
       <c r="B13" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Översjökölen, Dlr</t>
+          <t>Bryningen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>421412.66988439</v>
+        <v>421281</v>
       </c>
       <c r="R13" t="n">
-        <v>6841813.810478176</v>
+        <v>6841763</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1990,22 +1828,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,6 +1842,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2035,16 +1864,11 @@
         <v>100212744</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2072,10 +1896,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421491.6259464741</v>
+        <v>421491</v>
       </c>
       <c r="R14" t="n">
-        <v>6841899.799038227</v>
+        <v>6841900</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2105,19 +1929,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,15 +1958,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>100212648</v>
+        <v>100212688</v>
       </c>
       <c r="B15" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,37 +1969,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Översjökölen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421564.3899980612</v>
+        <v>421426</v>
       </c>
       <c r="R15" t="n">
-        <v>6841922.815428013</v>
+        <v>6841839</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2220,35 +2026,19 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Urskogsartad myr</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2258,7 +2048,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Andreas Öster, John-Olof Halvarsson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2268,12 +2058,7 @@
         <v>100212661</v>
       </c>
       <c r="B16" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,10 +2090,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421560.1149220391</v>
+        <v>421560</v>
       </c>
       <c r="R16" t="n">
-        <v>6841922.912892303</v>
+        <v>6841923</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2338,19 +2123,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,15 +2152,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>100212731</v>
+        <v>100212701</v>
       </c>
       <c r="B17" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2393,21 +2163,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2417,10 +2187,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421407.6804669152</v>
+        <v>421460</v>
       </c>
       <c r="R17" t="n">
-        <v>6841657.793075492</v>
+        <v>6841875</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2450,19 +2220,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,6 +2246,306 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>100212648</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Översjökölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>421564</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6841923</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Urskogsartad myr</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Andreas Öster, John-Olof Halvarsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>100212731</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Översjökölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>421407</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6841658</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>100212669</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Översjökölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>421413</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6841814</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 74075-2021 artfynd.xlsx
+++ b/artfynd/A 74075-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212646</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212647</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212667</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212684</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212687</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212689</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212705</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212713</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212747</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1660,6 +1710,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212758</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1757,6 +1812,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212741</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1858,6 +1918,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91502067</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1955,6 +2020,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212744</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2052,6 +2122,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212688</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2149,6 +2224,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212661</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2246,6 +2326,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212701</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2352,6 +2437,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212648</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2449,6 +2539,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212731</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2546,8 +2641,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212669</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>